--- a/data/raw/data_industry.xlsx
+++ b/data/raw/data_industry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celia\Documents\Industry Decarbonisation\pypsa_industry_coupled_soft-linked\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kande\Documents\GitHub\Industry_optimisation_model\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029217D0-486F-4000-BC52-1CCFB1079E83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560780B8-8624-4AA0-9903-6D9D91AD7B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="4665" activeTab="3" xr2:uid="{69F55029-E6FD-4DAD-9766-3BCD230AD838}"/>
+    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="17520" xr2:uid="{69F55029-E6FD-4DAD-9766-3BCD230AD838}"/>
   </bookViews>
   <sheets>
     <sheet name="prices" sheetId="5" r:id="rId1"/>
@@ -40,6 +40,18 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1608,10 +1620,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -10259,18 +10271,18 @@
       <c r="M18" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="N18" s="78" t="s">
+      <c r="N18" s="79" t="s">
         <v>280</v>
       </c>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
-      <c r="U18" s="78"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="79"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="79"/>
+      <c r="V18" s="79"/>
+      <c r="W18" s="79"/>
     </row>
     <row r="19" spans="13:23" ht="45" x14ac:dyDescent="0.25">
       <c r="M19" s="37"/>
@@ -10573,7 +10585,7 @@
       <c r="B7" s="17">
         <v>2020</v>
       </c>
-      <c r="C7" s="79">
+      <c r="C7" s="78">
         <v>22.368639000000002</v>
       </c>
       <c r="D7" s="18" t="s">

--- a/data/raw/data_industry.xlsx
+++ b/data/raw/data_industry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kande\Documents\GitHub\Industry_optimisation_model\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560780B8-8624-4AA0-9903-6D9D91AD7B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FA4688D-E305-4E77-84E4-96223AC9B23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="17520" xr2:uid="{69F55029-E6FD-4DAD-9766-3BCD230AD838}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="10" xr2:uid="{69F55029-E6FD-4DAD-9766-3BCD230AD838}"/>
   </bookViews>
   <sheets>
     <sheet name="prices" sheetId="5" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">prices!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -9008,11 +9009,11 @@
         <v>152</v>
       </c>
       <c r="C4" s="71">
-        <f t="shared" ref="C4:D4" si="0">160*C2+0</f>
+        <f>160*C2+0</f>
         <v>80</v>
       </c>
       <c r="D4" s="71">
-        <f t="shared" si="0"/>
+        <f>160*D2+0</f>
         <v>119.19999999999999</v>
       </c>
       <c r="E4" s="73">
@@ -9267,19 +9268,19 @@
         <v>0.95</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:F8" si="0">C2+C3</f>
+        <f>C2+C3</f>
         <v>0.7</v>
       </c>
       <c r="D8">
-        <f t="shared" si="0"/>
+        <f>D2+D3</f>
         <v>0.74499999999999988</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f>E2+E3</f>
         <v>0.5</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f>F2+F3</f>
         <v>0.65</v>
       </c>
     </row>
